--- a/data/trans_orig/P45C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P45C-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2007</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2007 (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>917286</t>
+          <t>916385</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>951523</t>
+          <t>952500</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1205179</t>
+          <t>1205838</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1239990</t>
+          <t>1241435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2134011</t>
+          <t>2132522</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2184392</t>
+          <t>2184959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>67244</t>
+          <t>66727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101224</t>
+          <t>101145</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>59820</t>
+          <t>58960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>92828</t>
+          <t>90366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>134924</t>
+          <t>135637</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>182718</t>
+          <t>183304</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,83%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5474</t>
+          <t>4771</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19522</t>
+          <t>18066</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>8095</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22333</t>
+          <t>23195</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15398</t>
+          <t>15847</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35599</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1336263</t>
+          <t>1336152</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1401239</t>
+          <t>1401002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,47 +1204,47 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,08%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
+          <t>82,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>1341643</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>1312429</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1369502</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>84,77%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>82,92%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1306</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1341643</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>1308727</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1366674</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>84,77%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>82,69%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2669549</t>
+          <t>2666438</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2753219</t>
+          <t>2755335</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>84,2%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>255890</t>
+          <t>255779</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>317952</t>
+          <t>318100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>185058</t>
+          <t>181934</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236054</t>
+          <t>236625</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>453996</t>
+          <t>452233</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>533209</t>
+          <t>536049</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24223</t>
+          <t>24552</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50135</t>
+          <t>50828</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>21196</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45310</t>
+          <t>44399</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52053</t>
+          <t>52228</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>86800</t>
+          <t>85940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>432282</t>
+          <t>431545</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>469565</t>
+          <t>468373</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>369937</t>
+          <t>366908</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>403962</t>
+          <t>401620</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,82%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>809021</t>
+          <t>813331</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>860989</t>
+          <t>861414</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73403</t>
+          <t>73402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108810</t>
+          <t>109325</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63905</t>
+          <t>64055</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95677</t>
+          <t>97111</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146813</t>
+          <t>146930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195364</t>
+          <t>191760</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4577</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>18848</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4930</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18085</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32463</t>
+          <t>31724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2715376</t>
+          <t>2710294</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2798029</t>
+          <t>2797571</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2914915</t>
+          <t>2913396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2990517</t>
+          <t>2986825</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5649348</t>
+          <t>5648749</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5766251</t>
+          <t>5766669</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418229</t>
+          <t>418862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>500237</t>
+          <t>500495</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327798</t>
+          <t>327905</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>400883</t>
+          <t>398378</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>770046</t>
+          <t>765457</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>875580</t>
+          <t>876218</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41158</t>
+          <t>41915</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71594</t>
+          <t>72746</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42023</t>
+          <t>43297</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71951</t>
+          <t>73097</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92764</t>
+          <t>91197</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>135990</t>
+          <t>133070</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2012</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2012 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>835714</t>
+          <t>835629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>876873</t>
+          <t>874566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1172543</t>
+          <t>1172324</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1216818</t>
+          <t>1215198</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2024398</t>
+          <t>2020294</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2082465</t>
+          <t>2079621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,88%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>80185</t>
+          <t>82776</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119170</t>
+          <t>120948</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88280</t>
+          <t>88324</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>129803</t>
+          <t>128372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177042</t>
+          <t>180093</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>232912</t>
+          <t>236698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18988</t>
+          <t>19580</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>12117</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30618</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>19982</t>
+          <t>20964</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>43503</t>
+          <t>44362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1528089</t>
+          <t>1529736</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1599536</t>
+          <t>1601649</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1430804</t>
+          <t>1432102</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1494861</t>
+          <t>1494693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2981865</t>
+          <t>2984642</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3077415</t>
+          <t>3078174</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,76%</t>
+          <t>80,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,37%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>323189</t>
+          <t>319655</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>394871</t>
+          <t>390356</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>223437</t>
+          <t>219222</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>283382</t>
+          <t>281361</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>561606</t>
+          <t>561781</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>653662</t>
+          <t>651629</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18648</t>
+          <t>18112</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40446</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16848</t>
+          <t>17088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>37797</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41336</t>
+          <t>40406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>71408</t>
+          <t>68349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>350205</t>
+          <t>351606</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>386845</t>
+          <t>387364</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,69%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>368837</t>
+          <t>367937</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>400797</t>
+          <t>400849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>730117</t>
+          <t>727846</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>780906</t>
+          <t>779187</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>82580</t>
+          <t>81898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119033</t>
+          <t>117967</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45097</t>
+          <t>45794</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>74114</t>
+          <t>75258</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134716</t>
+          <t>136418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>183464</t>
+          <t>182869</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>12118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5233</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19828</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>9403</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26943</t>
+          <t>25705</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2746249</t>
+          <t>2749576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2837159</t>
+          <t>2837280</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3001647</t>
+          <t>3007190</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3086442</t>
+          <t>3092296</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,29%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5771326</t>
+          <t>5777602</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5891488</t>
+          <t>5903447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,42%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>512962</t>
+          <t>509982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>600323</t>
+          <t>596428</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>379364</t>
+          <t>375348</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>456799</t>
+          <t>454855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>919691</t>
+          <t>910776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1035889</t>
+          <t>1031907</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32127</t>
+          <t>30927</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58062</t>
+          <t>58015</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42943</t>
+          <t>42496</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72738</t>
+          <t>72486</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>81717</t>
+          <t>81627</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122358</t>
+          <t>120863</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4648,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2016</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2016 (tasa de respuesta: 99,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>683070</t>
+          <t>681287</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>710520</t>
+          <t>709808</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>905021</t>
+          <t>904666</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>936575</t>
+          <t>936340</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1597311</t>
+          <t>1597622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1638603</t>
+          <t>1639644</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,71%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30119</t>
+          <t>30866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56119</t>
+          <t>57407</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>41463</t>
+          <t>40456</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70566</t>
+          <t>71115</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78632</t>
+          <t>78453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117551</t>
+          <t>117453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2912</t>
+          <t>2750</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14140</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,47 +5084,47 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>8115</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>3794</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>15541</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>0,39%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,91%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>8115</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3651</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>15918</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>8572</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>23856</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1702846</t>
+          <t>1705587</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1776302</t>
+          <t>1776970</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1629035</t>
+          <t>1631355</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1694913</t>
+          <t>1695172</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>82,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3358380</t>
+          <t>3358499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3449266</t>
+          <t>3449663</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,41%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>265977</t>
+          <t>266287</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>335754</t>
+          <t>333674</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>258867</t>
+          <t>259198</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>321426</t>
+          <t>319700</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>546207</t>
+          <t>544363</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>638469</t>
+          <t>634030</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,7%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11702</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>29992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>15268</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>36364</t>
+          <t>35430</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31641</t>
+          <t>30914</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57556</t>
+          <t>58575</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>436245</t>
+          <t>437247</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>474579</t>
+          <t>473210</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>425123</t>
+          <t>425933</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>462633</t>
+          <t>462653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>873592</t>
+          <t>873096</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>926204</t>
+          <t>922645</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,53%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,1%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63011</t>
+          <t>63884</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99688</t>
+          <t>98315</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>74787</t>
+          <t>75726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>111115</t>
+          <t>110801</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147535</t>
+          <t>150268</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>197660</t>
+          <t>200992</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,54%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>968</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12652</t>
+          <t>12657</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12701</t>
+          <t>11973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4905</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19493</t>
+          <t>19180</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2853893</t>
+          <t>2850683</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2934435</t>
+          <t>2932813</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2988946</t>
+          <t>2992087</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3071708</t>
+          <t>3072480</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5867084</t>
+          <t>5868321</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5975181</t>
+          <t>5985802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>384411</t>
+          <t>384937</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463318</t>
+          <t>464941</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>397896</t>
+          <t>399447</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>477374</t>
+          <t>474116</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>808747</t>
+          <t>802317</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>916382</t>
+          <t>915118</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20421</t>
+          <t>20839</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44350</t>
+          <t>44659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27428</t>
+          <t>27018</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52662</t>
+          <t>51942</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55475</t>
+          <t>52797</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87740</t>
+          <t>87391</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2023</t>
+          <t>Población según según si ha sufrido a lo largo de este último año alguna quemadura solar en 2023 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>420457</t>
+          <t>419079</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>451617</t>
+          <t>449460</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>672200</t>
+          <t>672823</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>697388</t>
+          <t>696625</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1100826</t>
+          <t>1100633</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1139825</t>
+          <t>1140665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51755</t>
+          <t>53335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80866</t>
+          <t>80261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50003</t>
+          <t>50255</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72693</t>
+          <t>72641</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109794</t>
+          <t>109446</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146347</t>
+          <t>146688</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>20248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4935</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7179,7 +7179,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13405</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30627</t>
+          <t>29523</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1855067</t>
+          <t>1856260</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2024071</t>
+          <t>2025888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1896581</t>
+          <t>1895993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2028381</t>
+          <t>2025855</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3777035</t>
+          <t>3774956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4003891</t>
+          <t>3990445</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,29%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>236320</t>
+          <t>238356</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>393814</t>
+          <t>392041</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>187922</t>
+          <t>183814</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>305998</t>
+          <t>303905</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>467872</t>
+          <t>473669</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>673401</t>
+          <t>671813</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19057</t>
+          <t>20089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49938</t>
+          <t>49448</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19421</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43385</t>
+          <t>44701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45348</t>
+          <t>45048</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83815</t>
+          <t>83353</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535876</t>
+          <t>537040</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>572929</t>
+          <t>574280</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,49 +7825,49 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
+          <t>88,81%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>570197</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>551822</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>585151</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>86,33%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>83,55%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
           <t>88,6%</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>882</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>570197</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>551367</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>586463</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>86,33%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>83,48%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>88,8%</t>
-        </is>
-      </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>1471</t>
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1101223</t>
+          <t>1098613</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1151576</t>
+          <t>1150823</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,04%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61721</t>
+          <t>62844</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98531</t>
+          <t>97355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63789</t>
+          <t>62762</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96519</t>
+          <t>93906</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>132666</t>
+          <t>131494</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180043</t>
+          <t>182069</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,93%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23576</t>
+          <t>25332</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>21954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16002</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39507</t>
+          <t>37369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2850396</t>
+          <t>2851397</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3024191</t>
+          <t>3033489</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3155459</t>
+          <t>3152226</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3281709</t>
+          <t>3282921</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6028577</t>
+          <t>6019063</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6231372</t>
+          <t>6238194</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>374465</t>
+          <t>367576</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>535568</t>
+          <t>535370</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327652</t>
+          <t>327687</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>441509</t>
+          <t>445658</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>768746</t>
+          <t>762278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>959401</t>
+          <t>962703</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39158</t>
+          <t>39939</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75917</t>
+          <t>76061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38939</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>67970</t>
+          <t>68003</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>84320</t>
+          <t>85157</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>130206</t>
+          <t>137168</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P45C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P45C-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>916385</t>
+          <t>915868</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>952500</t>
+          <t>953367</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1205838</t>
+          <t>1206070</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1241435</t>
+          <t>1240661</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2132522</t>
+          <t>2131141</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2184959</t>
+          <t>2184302</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66727</t>
+          <t>66038</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101145</t>
+          <t>101555</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58960</t>
+          <t>59843</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90366</t>
+          <t>92059</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>135637</t>
+          <t>134434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>183304</t>
+          <t>184972</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4771</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18066</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>7826</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>22884</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>15469</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>35784</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1336152</t>
+          <t>1334703</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1401002</t>
+          <t>1397034</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1312429</t>
+          <t>1311389</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1369502</t>
+          <t>1366996</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2666438</t>
+          <t>2664226</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2755335</t>
+          <t>2756150</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,22%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>255779</t>
+          <t>258829</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>318100</t>
+          <t>317443</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181934</t>
+          <t>183824</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236625</t>
+          <t>235385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>452233</t>
+          <t>452682</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>536049</t>
+          <t>538019</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24552</t>
+          <t>24664</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50828</t>
+          <t>49062</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>21949</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44399</t>
+          <t>44735</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52228</t>
+          <t>53599</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85940</t>
+          <t>86186</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>431545</t>
+          <t>427447</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>468373</t>
+          <t>466201</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>366908</t>
+          <t>368794</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>401620</t>
+          <t>401189</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>77,18%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>813331</t>
+          <t>809226</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>861414</t>
+          <t>860516</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,87%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73402</t>
+          <t>74754</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109325</t>
+          <t>110124</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64055</t>
+          <t>64315</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97111</t>
+          <t>96522</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>146930</t>
+          <t>147209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>191760</t>
+          <t>197170</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,22%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>19023</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4991</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18821</t>
+          <t>18326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31724</t>
+          <t>30350</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2710294</t>
+          <t>2711579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2797571</t>
+          <t>2796625</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2913396</t>
+          <t>2911106</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2986825</t>
+          <t>2990281</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5648749</t>
+          <t>5650892</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5766669</t>
+          <t>5759745</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,85%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>418862</t>
+          <t>417405</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>500495</t>
+          <t>501386</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327905</t>
+          <t>328046</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>398378</t>
+          <t>398532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>765457</t>
+          <t>771904</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>876218</t>
+          <t>871480</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41915</t>
+          <t>41443</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>72746</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>43297</t>
+          <t>42484</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>73097</t>
+          <t>72232</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>91197</t>
+          <t>92113</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>133070</t>
+          <t>136039</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>835629</t>
+          <t>835422</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>874566</t>
+          <t>875404</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1172324</t>
+          <t>1172341</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1215198</t>
+          <t>1215565</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2020294</t>
+          <t>2023310</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2079621</t>
+          <t>2079750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>82776</t>
+          <t>81673</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120948</t>
+          <t>119564</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>88324</t>
+          <t>88174</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128372</t>
+          <t>127279</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>180093</t>
+          <t>179653</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236698</t>
+          <t>235235</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5685</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19580</t>
+          <t>19335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12117</t>
+          <t>12019</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>30099</t>
+          <t>29614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>20964</t>
+          <t>20464</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>44362</t>
+          <t>41903</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1529736</t>
+          <t>1529037</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1601649</t>
+          <t>1599444</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1432102</t>
+          <t>1433207</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1494693</t>
+          <t>1493772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2984642</t>
+          <t>2983964</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3078174</t>
+          <t>3074651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,27%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>319655</t>
+          <t>324016</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>390356</t>
+          <t>390610</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>219222</t>
+          <t>222794</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>281361</t>
+          <t>281729</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>561781</t>
+          <t>561216</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>651629</t>
+          <t>650941</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18112</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>40663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17088</t>
+          <t>17282</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37797</t>
+          <t>37521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40406</t>
+          <t>40871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68349</t>
+          <t>69876</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>351606</t>
+          <t>348130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>387364</t>
+          <t>388032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>367937</t>
+          <t>368898</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>400849</t>
+          <t>399487</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>87,97%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>727846</t>
+          <t>728424</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>779187</t>
+          <t>779632</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>78,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>81898</t>
+          <t>82413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>117967</t>
+          <t>122091</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>45794</t>
+          <t>44964</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>75258</t>
+          <t>74755</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>136418</t>
+          <t>135882</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182869</t>
+          <t>183163</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,68%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>12005</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>19450</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9403</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>25705</t>
+          <t>26051</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4016,7 +4016,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2749576</t>
+          <t>2750093</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2837280</t>
+          <t>2844696</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3007190</t>
+          <t>3004655</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3092296</t>
+          <t>3088663</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5777602</t>
+          <t>5776132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5903447</t>
+          <t>5898729</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>509982</t>
+          <t>505005</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>596428</t>
+          <t>600015</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>375348</t>
+          <t>378626</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>454855</t>
+          <t>455178</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>910776</t>
+          <t>917198</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1031907</t>
+          <t>1033591</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30927</t>
+          <t>31167</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>58015</t>
+          <t>58731</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>42496</t>
+          <t>42861</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>72486</t>
+          <t>74166</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>81627</t>
+          <t>80241</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>120863</t>
+          <t>124677</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>681287</t>
+          <t>681199</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>709808</t>
+          <t>708842</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>904666</t>
+          <t>906105</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>936340</t>
+          <t>936328</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1597622</t>
+          <t>1595327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1639644</t>
+          <t>1638404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>31389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>57407</t>
+          <t>56877</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,47 +4971,47 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>4,21%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>7,62%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>54405</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>40760</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>70100</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,69%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>54405</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>40456</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>71115</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>5,52%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>78453</t>
+          <t>78365</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117453</t>
+          <t>116812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,75%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2750</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>13737</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15541</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23856</t>
+          <t>25412</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1705587</t>
+          <t>1709166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1776970</t>
+          <t>1772883</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1631355</t>
+          <t>1626843</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1695172</t>
+          <t>1693902</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3358499</t>
+          <t>3351310</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3449663</t>
+          <t>3452116</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,47%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>266287</t>
+          <t>269233</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>333674</t>
+          <t>332309</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>259198</t>
+          <t>262011</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>319700</t>
+          <t>325966</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>544363</t>
+          <t>542215</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>634030</t>
+          <t>640660</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29992</t>
+          <t>30506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15268</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>35930</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30914</t>
+          <t>31671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58575</t>
+          <t>57961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>437247</t>
+          <t>436728</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>473210</t>
+          <t>472223</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>425933</t>
+          <t>426914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>462653</t>
+          <t>463523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>873096</t>
+          <t>875511</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>922645</t>
+          <t>925681</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63884</t>
+          <t>66101</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>98315</t>
+          <t>100138</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75726</t>
+          <t>75072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>110801</t>
+          <t>110500</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>150268</t>
+          <t>148676</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200992</t>
+          <t>197148</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,18%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12657</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11973</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19180</t>
+          <t>20019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2850683</t>
+          <t>2852830</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2932813</t>
+          <t>2936260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2992087</t>
+          <t>2990348</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3072480</t>
+          <t>3074966</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5868321</t>
+          <t>5871298</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5985802</t>
+          <t>5985482</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,32%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>384937</t>
+          <t>381652</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>464941</t>
+          <t>462057</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>399447</t>
+          <t>395838</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>474116</t>
+          <t>477084</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>802317</t>
+          <t>803659</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>915118</t>
+          <t>912949</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,32%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>20112</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44659</t>
+          <t>43524</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27018</t>
+          <t>27692</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>51942</t>
+          <t>55014</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>52797</t>
+          <t>53766</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>87391</t>
+          <t>87398</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -6893,32 +6893,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>436801</t>
+          <t>494378</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>419079</t>
+          <t>477392</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>449460</t>
+          <t>511714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6928,32 +6928,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>685558</t>
+          <t>746669</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>672823</t>
+          <t>732590</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>696625</t>
+          <t>757526</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1122359</t>
+          <t>1241047</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1100633</t>
+          <t>1219851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1140665</t>
+          <t>1261795</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,19%</t>
         </is>
       </c>
     </row>
@@ -7006,32 +7006,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>65376</t>
+          <t>70805</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53335</t>
+          <t>56938</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>80261</t>
+          <t>88922</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7041,32 +7041,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60671</t>
+          <t>65952</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50255</t>
+          <t>55635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72641</t>
+          <t>79378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>126047</t>
+          <t>136757</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>109446</t>
+          <t>117491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>146688</t>
+          <t>157172</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -7119,32 +7119,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>12393</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20248</t>
+          <t>20980</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7154,32 +7154,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8686</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5408</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>14529</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13405</t>
+          <t>13746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29523</t>
+          <t>30856</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,21%</t>
         </is>
       </c>
     </row>
@@ -7232,17 +7232,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>513998</t>
+          <t>577576</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>513998</t>
+          <t>577576</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>513998</t>
+          <t>577576</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7267,17 +7267,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>754915</t>
+          <t>821429</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>754915</t>
+          <t>821429</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>754915</t>
+          <t>821429</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1268913</t>
+          <t>1399006</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1268913</t>
+          <t>1399006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1268913</t>
+          <t>1399006</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7349,32 +7349,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1919045</t>
+          <t>1815694</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1856260</t>
+          <t>1769373</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2025888</t>
+          <t>1861282</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7384,32 +7384,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1945360</t>
+          <t>1847359</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1895993</t>
+          <t>1813964</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2025855</t>
+          <t>1879033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3864404</t>
+          <t>3663053</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3774956</t>
+          <t>3606111</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3990445</t>
+          <t>3720883</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>84,72%</t>
         </is>
       </c>
     </row>
@@ -7462,32 +7462,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>333085</t>
+          <t>374011</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>238356</t>
+          <t>330928</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>392041</t>
+          <t>420360</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7497,32 +7497,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>259981</t>
+          <t>287152</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>183814</t>
+          <t>257390</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>303905</t>
+          <t>319138</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>593065</t>
+          <t>661163</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>473669</t>
+          <t>605755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>671813</t>
+          <t>713673</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>16,25%</t>
         </is>
       </c>
     </row>
@@ -7575,32 +7575,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>31851</t>
+          <t>34319</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20089</t>
+          <t>23379</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49448</t>
+          <t>50528</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7610,67 +7610,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>33289</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>23310</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44701</t>
+          <t>46165</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>67607</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>51102</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>87927</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,54%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>2,0%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>62273</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>45048</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>83353</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,38%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -7688,17 +7688,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2283981</t>
+          <t>2224024</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2283981</t>
+          <t>2224024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2283981</t>
+          <t>2224024</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7723,17 +7723,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2235762</t>
+          <t>2167799</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2235762</t>
+          <t>2167799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2235762</t>
+          <t>2167799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4519743</t>
+          <t>4391823</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4519743</t>
+          <t>4391823</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4519743</t>
+          <t>4391823</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7805,32 +7805,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>556739</t>
+          <t>604916</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>537040</t>
+          <t>580306</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>574280</t>
+          <t>624772</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7840,32 +7840,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>570197</t>
+          <t>633157</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>551822</t>
+          <t>615253</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>585151</t>
+          <t>650423</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,16%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1126936</t>
+          <t>1238073</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1098613</t>
+          <t>1210093</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1150823</t>
+          <t>1264788</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,44%</t>
         </is>
       </c>
     </row>
@@ -7918,32 +7918,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78268</t>
+          <t>93177</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62844</t>
+          <t>74486</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97355</t>
+          <t>116172</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7953,17 +7953,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>77678</t>
+          <t>86391</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62762</t>
+          <t>72156</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>93906</t>
+          <t>102781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>155946</t>
+          <t>179567</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>131494</t>
+          <t>156288</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>182069</t>
+          <t>207234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,33%</t>
         </is>
       </c>
     </row>
@@ -8031,32 +8031,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>11616</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6676</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25332</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8066,32 +8066,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>12588</t>
+          <t>15330</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>9092</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>24942</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>24204</t>
+          <t>28824</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>18202</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37369</t>
+          <t>42958</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -8144,17 +8144,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8261,32 +8261,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2912585</t>
+          <t>2914989</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2851397</t>
+          <t>2858816</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3033489</t>
+          <t>2965159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8296,32 +8296,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3201114</t>
+          <t>3227185</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3152226</t>
+          <t>3185937</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3282921</t>
+          <t>3262796</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>87,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>6113699</t>
+          <t>6142173</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6019063</t>
+          <t>6075620</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6238194</t>
+          <t>6210743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>85,82%</t>
         </is>
       </c>
     </row>
@@ -8374,32 +8374,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>476728</t>
+          <t>537993</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>367576</t>
+          <t>491324</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>535370</t>
+          <t>591722</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8409,32 +8409,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>398330</t>
+          <t>439494</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>327687</t>
+          <t>405995</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>445658</t>
+          <t>477605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>875058</t>
+          <t>977487</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>762278</t>
+          <t>912954</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>962703</t>
+          <t>1047530</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,47%</t>
         </is>
       </c>
     </row>
@@ -8487,32 +8487,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>55289</t>
+          <t>60206</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39939</t>
+          <t>45309</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>76061</t>
+          <t>79984</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8522,32 +8522,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>51696</t>
+          <t>57427</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>38939</t>
+          <t>45367</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>68003</t>
+          <t>74276</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>106985</t>
+          <t>117633</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>85157</t>
+          <t>97270</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>137168</t>
+          <t>142701</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,97%</t>
         </is>
       </c>
     </row>
@@ -8600,17 +8600,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3444602</t>
+          <t>3513188</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3444602</t>
+          <t>3513188</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3444602</t>
+          <t>3513188</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8635,17 +8635,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3651140</t>
+          <t>3724106</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3651140</t>
+          <t>3724106</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3651140</t>
+          <t>3724106</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>7095742</t>
+          <t>7237293</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7095742</t>
+          <t>7237293</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7095742</t>
+          <t>7237293</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
